--- a/data/nzd0520/nzd0520.xlsx
+++ b/data/nzd0520/nzd0520.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M377"/>
+  <dimension ref="A1:M380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17238,7 +17238,7 @@
         <v>299.66</v>
       </c>
       <c r="C376" t="n">
-        <v>279.02</v>
+        <v>287.57</v>
       </c>
       <c r="D376" t="n">
         <v>263.84</v>
@@ -17253,7 +17253,7 @@
         <v>302.88</v>
       </c>
       <c r="H376" t="n">
-        <v>309.8</v>
+        <v>315.29</v>
       </c>
       <c r="I376" t="n">
         <v>316.18</v>
@@ -17283,7 +17283,7 @@
         <v>298.23</v>
       </c>
       <c r="C377" t="n">
-        <v>274.2</v>
+        <v>287.57</v>
       </c>
       <c r="D377" t="n">
         <v>260.23</v>
@@ -17298,7 +17298,7 @@
         <v>300.33</v>
       </c>
       <c r="H377" t="n">
-        <v>305.76</v>
+        <v>315.29</v>
       </c>
       <c r="I377" t="n">
         <v>308.25</v>
@@ -17313,6 +17313,141 @@
         <v>309.51</v>
       </c>
       <c r="M377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:26:28+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>299.58</v>
+      </c>
+      <c r="C378" t="n">
+        <v>293.41</v>
+      </c>
+      <c r="D378" t="n">
+        <v>261.9</v>
+      </c>
+      <c r="E378" t="n">
+        <v>277.39</v>
+      </c>
+      <c r="F378" t="n">
+        <v>274.24</v>
+      </c>
+      <c r="G378" t="n">
+        <v>297.56</v>
+      </c>
+      <c r="H378" t="n">
+        <v>317.53</v>
+      </c>
+      <c r="I378" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="J378" t="n">
+        <v>306.6</v>
+      </c>
+      <c r="K378" t="n">
+        <v>304.66</v>
+      </c>
+      <c r="L378" t="n">
+        <v>295.35</v>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-08 22:32:39+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>299.58</v>
+      </c>
+      <c r="C379" t="n">
+        <v>293.41</v>
+      </c>
+      <c r="D379" t="n">
+        <v>257.65</v>
+      </c>
+      <c r="E379" t="n">
+        <v>273.91</v>
+      </c>
+      <c r="F379" t="n">
+        <v>272.46</v>
+      </c>
+      <c r="G379" t="n">
+        <v>294.49</v>
+      </c>
+      <c r="H379" t="n">
+        <v>317.53</v>
+      </c>
+      <c r="I379" t="n">
+        <v>288.6</v>
+      </c>
+      <c r="J379" t="n">
+        <v>299.53</v>
+      </c>
+      <c r="K379" t="n">
+        <v>298.46</v>
+      </c>
+      <c r="L379" t="n">
+        <v>287.62</v>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-24 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>286.15</v>
+      </c>
+      <c r="C380" t="n">
+        <v>274.97</v>
+      </c>
+      <c r="D380" t="n">
+        <v>254.82</v>
+      </c>
+      <c r="E380" t="n">
+        <v>270.84</v>
+      </c>
+      <c r="F380" t="n">
+        <v>270.27</v>
+      </c>
+      <c r="G380" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="H380" t="n">
+        <v>300.55</v>
+      </c>
+      <c r="I380" t="n">
+        <v>285.18</v>
+      </c>
+      <c r="J380" t="n">
+        <v>296.1</v>
+      </c>
+      <c r="K380" t="n">
+        <v>295.07</v>
+      </c>
+      <c r="L380" t="n">
+        <v>283.04</v>
+      </c>
+      <c r="M380" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17329,7 +17464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B408"/>
+  <dimension ref="A1:B412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21412,6 +21547,46 @@
       </c>
       <c r="B408" t="n">
         <v>-0.86</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-07-08 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-07-24 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -21580,28 +21755,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4859050702389542</v>
+        <v>-0.4592007606727698</v>
       </c>
       <c r="J2" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K2" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06349251077713491</v>
+        <v>0.05736590259063079</v>
       </c>
       <c r="M2" t="n">
-        <v>10.55557286942964</v>
+        <v>10.59871519323932</v>
       </c>
       <c r="N2" t="n">
-        <v>205.3117451116833</v>
+        <v>206.299214410097</v>
       </c>
       <c r="O2" t="n">
-        <v>14.32870353910929</v>
+        <v>14.36311993997463</v>
       </c>
       <c r="P2" t="n">
-        <v>290.9694647400113</v>
+        <v>290.6977247931713</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21658,28 +21833,28 @@
         <v>0.1275</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6348246881715714</v>
+        <v>-0.5657057866294917</v>
       </c>
       <c r="J3" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08044444844285248</v>
+        <v>0.06292203307934019</v>
       </c>
       <c r="M3" t="n">
-        <v>12.89386240806707</v>
+        <v>13.06803919602371</v>
       </c>
       <c r="N3" t="n">
-        <v>271.0903245099727</v>
+        <v>283.394805023614</v>
       </c>
       <c r="O3" t="n">
-        <v>16.46482081621214</v>
+        <v>16.8343341128663</v>
       </c>
       <c r="P3" t="n">
-        <v>268.5436217801337</v>
+        <v>267.8433749390061</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21736,28 +21911,28 @@
         <v>0.0459</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06231428061561167</v>
+        <v>-0.04112072381341905</v>
       </c>
       <c r="J4" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K4" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002505182652497551</v>
+        <v>0.001094036163835521</v>
       </c>
       <c r="M4" t="n">
-        <v>7.420609609152086</v>
+        <v>7.471583007568835</v>
       </c>
       <c r="N4" t="n">
-        <v>89.28026703504946</v>
+        <v>90.06525241896092</v>
       </c>
       <c r="O4" t="n">
-        <v>9.448823579422438</v>
+        <v>9.490271461816091</v>
       </c>
       <c r="P4" t="n">
-        <v>246.2198637862381</v>
+        <v>246.0027556317839</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21814,28 +21989,28 @@
         <v>0.1024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4107619217642271</v>
+        <v>0.4487159294853442</v>
       </c>
       <c r="J5" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08254885197967032</v>
+        <v>0.09487560396974459</v>
       </c>
       <c r="M5" t="n">
-        <v>8.431287234197354</v>
+        <v>8.595487997416853</v>
       </c>
       <c r="N5" t="n">
-        <v>108.2832598535496</v>
+        <v>112.0571397967764</v>
       </c>
       <c r="O5" t="n">
-        <v>10.40592426714464</v>
+        <v>10.58570450167472</v>
       </c>
       <c r="P5" t="n">
-        <v>238.7417969714095</v>
+        <v>238.3529512641788</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21892,28 +22067,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3429929184946538</v>
+        <v>-0.3342954176499936</v>
       </c>
       <c r="J6" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K6" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0773641479253353</v>
+        <v>0.07480435159756926</v>
       </c>
       <c r="M6" t="n">
-        <v>6.963059697841562</v>
+        <v>6.953113211956754</v>
       </c>
       <c r="N6" t="n">
-        <v>81.01584089116363</v>
+        <v>80.63255231968952</v>
       </c>
       <c r="O6" t="n">
-        <v>9.000880006486234</v>
+        <v>8.979563036122054</v>
       </c>
       <c r="P6" t="n">
-        <v>275.939081273916</v>
+        <v>275.8499920875472</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21970,28 +22145,28 @@
         <v>0.0809</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2693621495243615</v>
+        <v>-0.25496363708033</v>
       </c>
       <c r="J7" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K7" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06975216208842261</v>
+        <v>0.0632763634022242</v>
       </c>
       <c r="M7" t="n">
-        <v>5.769448900181104</v>
+        <v>5.788673013028069</v>
       </c>
       <c r="N7" t="n">
-        <v>55.73167457673656</v>
+        <v>55.99663207605762</v>
       </c>
       <c r="O7" t="n">
-        <v>7.465364999565431</v>
+        <v>7.48308974128051</v>
       </c>
       <c r="P7" t="n">
-        <v>292.4795542467927</v>
+        <v>292.3319100615136</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22048,28 +22223,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2464242458274965</v>
+        <v>-0.2134231554199705</v>
       </c>
       <c r="J8" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01908132184658384</v>
+        <v>0.01434543464250426</v>
       </c>
       <c r="M8" t="n">
-        <v>9.662305101675249</v>
+        <v>9.722179871482075</v>
       </c>
       <c r="N8" t="n">
-        <v>180.2337548430918</v>
+        <v>182.5452669503164</v>
       </c>
       <c r="O8" t="n">
-        <v>13.42511656720685</v>
+        <v>13.51093138722555</v>
       </c>
       <c r="P8" t="n">
-        <v>302.2718579934901</v>
+        <v>301.9342962401942</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22130,28 +22305,28 @@
         <v>0.1729</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4389694499826695</v>
+        <v>-0.4631539401912234</v>
       </c>
       <c r="J9" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K9" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04408127702697051</v>
+        <v>0.04928848164522914</v>
       </c>
       <c r="M9" t="n">
-        <v>11.21591870702746</v>
+        <v>11.27463208612295</v>
       </c>
       <c r="N9" t="n">
-        <v>243.0175392993903</v>
+        <v>243.0797732231912</v>
       </c>
       <c r="O9" t="n">
-        <v>15.58901983125913</v>
+        <v>15.59101578548336</v>
       </c>
       <c r="P9" t="n">
-        <v>316.754752696228</v>
+        <v>317.001612871039</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22212,28 +22387,28 @@
         <v>0.1334</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.498295935558017</v>
+        <v>-0.5171812642651947</v>
       </c>
       <c r="J10" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K10" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06959098815993614</v>
+        <v>0.07535650234483859</v>
       </c>
       <c r="M10" t="n">
-        <v>10.56240185612048</v>
+        <v>10.58495264086914</v>
       </c>
       <c r="N10" t="n">
-        <v>192.7360031716492</v>
+        <v>192.5016969268251</v>
       </c>
       <c r="O10" t="n">
-        <v>13.88293928430321</v>
+        <v>13.87449807837477</v>
       </c>
       <c r="P10" t="n">
-        <v>326.2583157300534</v>
+        <v>326.4509080013398</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22290,28 +22465,28 @@
         <v>0.1563</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.04312426895092123</v>
+        <v>-0.07697629954119786</v>
       </c>
       <c r="J11" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K11" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002919346224491415</v>
+        <v>0.0009368880160668391</v>
       </c>
       <c r="M11" t="n">
-        <v>14.77001061016384</v>
+        <v>14.86955159943157</v>
       </c>
       <c r="N11" t="n">
-        <v>369.7416185050744</v>
+        <v>370.6079294666391</v>
       </c>
       <c r="O11" t="n">
-        <v>19.22866658156707</v>
+        <v>19.2511799499833</v>
       </c>
       <c r="P11" t="n">
-        <v>322.3606401779741</v>
+        <v>322.7057998182416</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22368,28 +22543,28 @@
         <v>0.1938</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5057294017107751</v>
+        <v>0.4498345213987011</v>
       </c>
       <c r="J12" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K12" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02502037480235542</v>
+        <v>0.01992401889196882</v>
       </c>
       <c r="M12" t="n">
-        <v>18.49496501791561</v>
+        <v>18.68995072937264</v>
       </c>
       <c r="N12" t="n">
-        <v>567.572715077389</v>
+        <v>572.7936007489618</v>
       </c>
       <c r="O12" t="n">
-        <v>23.82378465058373</v>
+        <v>23.93310679266196</v>
       </c>
       <c r="P12" t="n">
-        <v>310.0372631942655</v>
+        <v>310.6159593693768</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22427,7 +22602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M377"/>
+  <dimension ref="A1:M380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47368,7 +47543,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>-46.2202406155333,166.77751609151102</t>
+          <t>-46.22029573297103,166.7774391811896</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -47393,7 +47568,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>-46.21840106377294,166.7738482807201</t>
+          <t>-46.218436453810725,166.7737988964732</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -47435,7 +47610,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>-46.22020954345425,166.77755944907412</t>
+          <t>-46.22029573297103,166.7774391811896</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -47460,7 +47635,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>-46.21837502081494,166.77388462172797</t>
+          <t>-46.218436453810725,166.7737988964732</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -47484,6 +47659,207 @@
         </is>
       </c>
       <c r="M377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:26:28+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-46.220780740533804,166.77800933347427</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-46.22033338040281,166.77738664820257</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-46.219722664540726,166.77699190393818</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-46.21941492955819,166.77617437931116</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-46.21898702982996,166.7755245271218</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-46.2187297617488,166.7746365699293</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>-46.21845089345475,166.77377874696248</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>-46.217894832313,166.77330772168685</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>-46.21756522504658,166.77252069237332</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>-46.217145109624745,166.7718599564607</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>-46.21667748331043,166.77126551500774</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-08 22:32:39+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-46.220780740533804,166.77800933347427</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-46.22033338040281,166.77738664820257</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-46.21969526706104,166.7770301339074</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-46.21939249603272,166.77620568294864</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-46.21897555527387,166.77554053870384</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-46.218709971534714,166.77466418548948</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>-46.21845089345475,166.77377874696248</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>-46.21785679942256,166.77336079361515</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>-46.217519650371955,166.77258428874893</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>-46.21710514337351,166.77191572681494</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>-46.21662765464521,166.77133504770737</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-24 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-46.2206941638572,166.77813014172284</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-46.2202145072524,166.77755252266175</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-46.21967702355459,166.77705559054797</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-46.219372705529324,166.77623329849254</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-46.218961437698496,166.77556023833765</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-46.21869005238637,166.77469198093544</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>-46.218341435693404,166.7739314871845</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>-46.21783475322553,166.77339155730925</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>-46.217497539871474,166.77261514239788</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>-46.2170832908454,166.77194622057092</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>-46.216598131299094,166.7713762455472</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0520/nzd0520.xlsx
+++ b/data/nzd0520/nzd0520.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M380"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17418,7 +17418,7 @@
         <v>286.15</v>
       </c>
       <c r="C380" t="n">
-        <v>274.97</v>
+        <v>293.41</v>
       </c>
       <c r="D380" t="n">
         <v>254.82</v>
@@ -17433,7 +17433,7 @@
         <v>291.4</v>
       </c>
       <c r="H380" t="n">
-        <v>300.55</v>
+        <v>317.53</v>
       </c>
       <c r="I380" t="n">
         <v>285.18</v>
@@ -17450,6 +17450,96 @@
       <c r="M380" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-09 22:32:57+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>286.15</v>
+      </c>
+      <c r="C381" t="n">
+        <v>285.16</v>
+      </c>
+      <c r="D381" t="n">
+        <v>255.32</v>
+      </c>
+      <c r="E381" t="n">
+        <v>269.48</v>
+      </c>
+      <c r="F381" t="n">
+        <v>271.15</v>
+      </c>
+      <c r="G381" t="n">
+        <v>290.92</v>
+      </c>
+      <c r="H381" t="n">
+        <v>309.12</v>
+      </c>
+      <c r="I381" t="n">
+        <v>282.25</v>
+      </c>
+      <c r="J381" t="n">
+        <v>294.08</v>
+      </c>
+      <c r="K381" t="n">
+        <v>292.87</v>
+      </c>
+      <c r="L381" t="n">
+        <v>279.86</v>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>286.15</v>
+      </c>
+      <c r="C382" t="n">
+        <v>274.7</v>
+      </c>
+      <c r="D382" t="n">
+        <v>255.85</v>
+      </c>
+      <c r="E382" t="n">
+        <v>268.68</v>
+      </c>
+      <c r="F382" t="n">
+        <v>270.51</v>
+      </c>
+      <c r="G382" t="n">
+        <v>290.52</v>
+      </c>
+      <c r="H382" t="n">
+        <v>299.37</v>
+      </c>
+      <c r="I382" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="J382" t="n">
+        <v>292.84</v>
+      </c>
+      <c r="K382" t="n">
+        <v>292.04</v>
+      </c>
+      <c r="L382" t="n">
+        <v>278.46</v>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -17464,7 +17554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B412"/>
+  <dimension ref="A1:B414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21587,6 +21677,26 @@
       </c>
       <c r="B412" t="n">
         <v>0.38</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>
@@ -21755,28 +21865,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4592007606727698</v>
+        <v>-0.451186064410537</v>
       </c>
       <c r="J2" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K2" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05736590259063079</v>
+        <v>0.05603255831173393</v>
       </c>
       <c r="M2" t="n">
-        <v>10.59871519323932</v>
+        <v>10.5804684657397</v>
       </c>
       <c r="N2" t="n">
-        <v>206.299214410097</v>
+        <v>205.5068166403791</v>
       </c>
       <c r="O2" t="n">
-        <v>14.36311993997463</v>
+        <v>14.33550894249587</v>
       </c>
       <c r="P2" t="n">
-        <v>290.6977247931713</v>
+        <v>290.6158385536424</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21833,28 +21943,28 @@
         <v>0.1275</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5657057866294917</v>
+        <v>-0.5269764486095876</v>
       </c>
       <c r="J3" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06292203307934019</v>
+        <v>0.05436286561954196</v>
       </c>
       <c r="M3" t="n">
-        <v>13.06803919602371</v>
+        <v>13.15812631037725</v>
       </c>
       <c r="N3" t="n">
-        <v>283.394805023614</v>
+        <v>289.1908215111039</v>
       </c>
       <c r="O3" t="n">
-        <v>16.8343341128663</v>
+        <v>17.00561147124983</v>
       </c>
       <c r="P3" t="n">
-        <v>267.8433749390061</v>
+        <v>267.449275621982</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21911,28 +22021,28 @@
         <v>0.0459</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04112072381341905</v>
+        <v>-0.03010417114487295</v>
       </c>
       <c r="J4" t="n">
+        <v>381</v>
+      </c>
+      <c r="K4" t="n">
         <v>379</v>
       </c>
-      <c r="K4" t="n">
-        <v>377</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.001094036163835521</v>
+        <v>0.0005898111635532777</v>
       </c>
       <c r="M4" t="n">
-        <v>7.471583007568835</v>
+        <v>7.489754356200569</v>
       </c>
       <c r="N4" t="n">
-        <v>90.06525241896092</v>
+        <v>90.18271720966123</v>
       </c>
       <c r="O4" t="n">
-        <v>9.490271461816091</v>
+        <v>9.49645814025741</v>
       </c>
       <c r="P4" t="n">
-        <v>246.0027556317839</v>
+        <v>245.8894820697971</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21989,28 +22099,28 @@
         <v>0.1024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4487159294853442</v>
+        <v>0.4679554839373578</v>
       </c>
       <c r="J5" t="n">
+        <v>381</v>
+      </c>
+      <c r="K5" t="n">
         <v>379</v>
       </c>
-      <c r="K5" t="n">
-        <v>377</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.09487560396974459</v>
+        <v>0.1019570855789784</v>
       </c>
       <c r="M5" t="n">
-        <v>8.595487997416853</v>
+        <v>8.668249466260509</v>
       </c>
       <c r="N5" t="n">
-        <v>112.0571397967764</v>
+        <v>113.2734018559824</v>
       </c>
       <c r="O5" t="n">
-        <v>10.58570450167472</v>
+        <v>10.64299778520988</v>
       </c>
       <c r="P5" t="n">
-        <v>238.3529512641788</v>
+        <v>238.1551283213113</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22067,28 +22177,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3342954176499936</v>
+        <v>-0.3302102553432267</v>
       </c>
       <c r="J6" t="n">
+        <v>381</v>
+      </c>
+      <c r="K6" t="n">
         <v>379</v>
       </c>
-      <c r="K6" t="n">
-        <v>377</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.07480435159756926</v>
+        <v>0.07386494577982683</v>
       </c>
       <c r="M6" t="n">
-        <v>6.953113211956754</v>
+        <v>6.937785033070837</v>
       </c>
       <c r="N6" t="n">
-        <v>80.63255231968952</v>
+        <v>80.28903473836954</v>
       </c>
       <c r="O6" t="n">
-        <v>8.979563036122054</v>
+        <v>8.960414875348659</v>
       </c>
       <c r="P6" t="n">
-        <v>275.8499920875472</v>
+        <v>275.807988202507</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22145,28 +22255,28 @@
         <v>0.0809</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.25496363708033</v>
+        <v>-0.2495587768852208</v>
       </c>
       <c r="J7" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K7" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0632763634022242</v>
+        <v>0.06132310435112187</v>
       </c>
       <c r="M7" t="n">
-        <v>5.788673013028069</v>
+        <v>5.782300848277411</v>
       </c>
       <c r="N7" t="n">
-        <v>55.99663207605762</v>
+        <v>55.84426887927619</v>
       </c>
       <c r="O7" t="n">
-        <v>7.48308974128051</v>
+        <v>7.472902306284767</v>
       </c>
       <c r="P7" t="n">
-        <v>292.3319100615136</v>
+        <v>292.2762791006323</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22223,28 +22333,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2134231554199705</v>
+        <v>-0.1964106624718966</v>
       </c>
       <c r="J8" t="n">
+        <v>381</v>
+      </c>
+      <c r="K8" t="n">
         <v>379</v>
       </c>
-      <c r="K8" t="n">
-        <v>377</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01434543464250426</v>
+        <v>0.01221514129665457</v>
       </c>
       <c r="M8" t="n">
-        <v>9.722179871482075</v>
+        <v>9.745009572796908</v>
       </c>
       <c r="N8" t="n">
-        <v>182.5452669503164</v>
+        <v>183.1747123525718</v>
       </c>
       <c r="O8" t="n">
-        <v>13.51093138722555</v>
+        <v>13.5342052722933</v>
       </c>
       <c r="P8" t="n">
-        <v>301.9342962401942</v>
+        <v>301.7595162111359</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22305,28 +22415,28 @@
         <v>0.1729</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4631539401912234</v>
+        <v>-0.4868537342281624</v>
       </c>
       <c r="J9" t="n">
+        <v>381</v>
+      </c>
+      <c r="K9" t="n">
         <v>379</v>
       </c>
-      <c r="K9" t="n">
-        <v>377</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.04928848164522914</v>
+        <v>0.05420567358168715</v>
       </c>
       <c r="M9" t="n">
-        <v>11.27463208612295</v>
+        <v>11.36300850536283</v>
       </c>
       <c r="N9" t="n">
-        <v>243.0797732231912</v>
+        <v>244.5757161474603</v>
       </c>
       <c r="O9" t="n">
-        <v>15.59101578548336</v>
+        <v>15.63891671911646</v>
       </c>
       <c r="P9" t="n">
-        <v>317.001612871039</v>
+        <v>317.244311938325</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22387,28 +22497,28 @@
         <v>0.1334</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5171812642651947</v>
+        <v>-0.536731868106561</v>
       </c>
       <c r="J10" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K10" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07535650234483859</v>
+        <v>0.08085173601650097</v>
       </c>
       <c r="M10" t="n">
-        <v>10.58495264086914</v>
+        <v>10.64001910209839</v>
       </c>
       <c r="N10" t="n">
-        <v>192.5016969268251</v>
+        <v>193.3745727105144</v>
       </c>
       <c r="O10" t="n">
-        <v>13.87449807837477</v>
+        <v>13.9059186215983</v>
       </c>
       <c r="P10" t="n">
-        <v>326.4509080013398</v>
+        <v>326.6509061966294</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22465,28 +22575,28 @@
         <v>0.1563</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07697629954119786</v>
+        <v>-0.105829469014304</v>
       </c>
       <c r="J11" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K11" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0009368880160668391</v>
+        <v>0.001770929312869152</v>
       </c>
       <c r="M11" t="n">
-        <v>14.86955159943157</v>
+        <v>14.98215202748291</v>
       </c>
       <c r="N11" t="n">
-        <v>370.6079294666391</v>
+        <v>372.7611150315514</v>
       </c>
       <c r="O11" t="n">
-        <v>19.2511799499833</v>
+        <v>19.30702242790305</v>
       </c>
       <c r="P11" t="n">
-        <v>322.7057998182416</v>
+        <v>323.0009608171113</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22543,28 +22653,28 @@
         <v>0.1938</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4498345213987011</v>
+        <v>0.4038640542134673</v>
       </c>
       <c r="J12" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K12" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01992401889196882</v>
+        <v>0.01603974500572625</v>
       </c>
       <c r="M12" t="n">
-        <v>18.68995072937264</v>
+        <v>18.87858373147969</v>
       </c>
       <c r="N12" t="n">
-        <v>572.7936007489618</v>
+        <v>579.715982370141</v>
       </c>
       <c r="O12" t="n">
-        <v>23.93310679266196</v>
+        <v>24.07729184044877</v>
       </c>
       <c r="P12" t="n">
-        <v>310.6159593693768</v>
+        <v>311.0934684913131</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22602,7 +22712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M380"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47811,7 +47921,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>-46.2202145072524,166.77755252266175</t>
+          <t>-46.22033338040281,166.77738664820257</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -47836,7 +47946,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>-46.218341435693404,166.7739314871845</t>
+          <t>-46.21845089345475,166.77377874696248</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -47862,6 +47972,140 @@
       <c r="M380" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-09 22:32:57+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-46.2206941638572,166.77813014172284</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-46.220280196950796,166.77746086002105</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-46.21968024678942,166.77705109290955</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-46.2193639383983,166.77624553208213</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-46.21896711051465,166.77555232250427</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>-46.21868695814905,166.77469629867278</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>-46.21839668030569,166.77385439752584</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>-46.217815865686546,166.77341791331986</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>-46.21748451852265,166.7726333127567</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>-46.217069109258695,166.77196601001603</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>-46.21657763254648,166.77140485013467</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-46.2206941638572,166.77813014172284</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-46.22021276669985,166.7775549514039</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-46.21968366341811,166.7770463254122</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-46.2193587812617,166.7762527283095</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-46.21896298483025,166.77555807947417</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-46.2186843796178,166.77469989678687</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>-46.218333829079285,166.77394210161773</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>-46.21780522935603,166.77343275543387</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>-46.217476525217755,166.7726444668341</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>-46.21706375893175,166.77197347603126</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>-46.216568607935784,166.7714174433425</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
